--- a/test_doc/new_org/syllabus_6_social_studies.xlsx
+++ b/test_doc/new_org/syllabus_6_social_studies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,16 +441,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>History: What, Where, How and When</t>
+          <t>Geography: Motions of the Earth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sources of history</t>
+          <t>Rotation and revolution</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -461,22 +461,22 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Timelines</t>
+          <t>Seasons</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>History: Earliest Societies</t>
+          <t>Maps and Globes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hunter-gatherers</t>
+          <t>Reading a map</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -491,22 +491,22 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tools and cave art</t>
+          <t>Directions and symbols</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Geography: The Earth in the Solar System</t>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Planets and satellites</t>
+          <t>Land and soil</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -521,26 +521,26 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>The moon</t>
+          <t>Forests and wildlife</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Geography: Globe — Latitudes and Longitudes</t>
+          <t>Geography: The Earth in the Solar System</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The grid</t>
+          <t>Planets and satellites</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -551,26 +551,26 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Heat zones</t>
+          <t>The moon</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Civics: Understanding Diversity</t>
+          <t>Geography: Maps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diversity around us</t>
+          <t>Kinds of maps</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unity in diversity</t>
+          <t>Map reading</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -591,16 +591,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>History: First Farmers and Herders</t>
+          <t>Transport and Communication</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Beginnings of agriculture</t>
+          <t>Means of transport</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -611,26 +611,26 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Settled life</t>
+          <t>Staying in touch</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geography: Motions of the Earth</t>
+          <t>History: Earliest Societies</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rotation and revolution</t>
+          <t>Hunter-gatherers</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -641,26 +641,26 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Seasons</t>
+          <t>Tools and cave art</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Civics: Government</t>
+          <t>History: First Farmers and Herders</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Levels of government</t>
+          <t>Beginnings of agriculture</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Democratic government</t>
+          <t>Settled life</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -681,16 +681,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>History: Kingdoms and an Early Republic</t>
+          <t>The Environment</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Janapadas</t>
+          <t>Pollution</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -701,70 +701,10 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mahajanapadas</t>
+          <t>Protecting nature</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Geography: Maps</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Kinds of maps</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Map reading</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Civics: Panchayati Raj</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Gram sabha</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Panchayat work</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
         <v>3</v>
       </c>
     </row>
